--- a/applications/pilot_study/negative/neg_lipid_reference_set.xlsx
+++ b/applications/pilot_study/negative/neg_lipid_reference_set.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/pilot_study/negative/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D1B4F3-9A9F-FD47-9191-1E444CC8F9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17040" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -638,7 +638,7 @@
         <v>1.64</v>
       </c>
       <c r="E2">
-        <f>D2*60</f>
+        <f t="shared" ref="E2:E22" si="0">D2*60</f>
         <v>98.399999999999991</v>
       </c>
       <c r="F2" t="s">
@@ -659,7 +659,7 @@
         <v>2.56</v>
       </c>
       <c r="E3">
-        <f>D3*60</f>
+        <f t="shared" si="0"/>
         <v>153.6</v>
       </c>
       <c r="F3" t="s">
@@ -680,7 +680,7 @@
         <v>2.67</v>
       </c>
       <c r="E4">
-        <f>D4*60</f>
+        <f t="shared" si="0"/>
         <v>160.19999999999999</v>
       </c>
       <c r="F4" t="s">
@@ -701,7 +701,7 @@
         <v>2.72</v>
       </c>
       <c r="E5">
-        <f>D5*60</f>
+        <f t="shared" si="0"/>
         <v>163.20000000000002</v>
       </c>
       <c r="F5" t="s">
@@ -722,7 +722,7 @@
         <v>2.83</v>
       </c>
       <c r="E6">
-        <f>D6*60</f>
+        <f t="shared" si="0"/>
         <v>169.8</v>
       </c>
       <c r="F6" t="s">
@@ -743,7 +743,7 @@
         <v>2.84</v>
       </c>
       <c r="E7">
-        <f>D7*60</f>
+        <f t="shared" si="0"/>
         <v>170.39999999999998</v>
       </c>
       <c r="F7" t="s">
@@ -764,7 +764,7 @@
         <v>3.44</v>
       </c>
       <c r="E8">
-        <f>D8*60</f>
+        <f t="shared" si="0"/>
         <v>206.4</v>
       </c>
       <c r="F8" t="s">
@@ -785,7 +785,7 @@
         <v>3.5209999999999999</v>
       </c>
       <c r="E9">
-        <f>D9*60</f>
+        <f t="shared" si="0"/>
         <v>211.26</v>
       </c>
       <c r="F9" t="s">
@@ -806,7 +806,7 @@
         <v>3.65</v>
       </c>
       <c r="E10">
-        <f>D10*60</f>
+        <f t="shared" si="0"/>
         <v>219</v>
       </c>
       <c r="F10" t="s">
@@ -827,7 +827,7 @@
         <v>6.34</v>
       </c>
       <c r="E11">
-        <f>D11*60</f>
+        <f t="shared" si="0"/>
         <v>380.4</v>
       </c>
       <c r="F11" t="s">
@@ -848,7 +848,7 @@
         <v>6.37</v>
       </c>
       <c r="E12">
-        <f>D12*60</f>
+        <f t="shared" si="0"/>
         <v>382.2</v>
       </c>
       <c r="F12" t="s">
@@ -869,7 +869,7 @@
         <v>7.46</v>
       </c>
       <c r="E13">
-        <f>D13*60</f>
+        <f t="shared" si="0"/>
         <v>447.6</v>
       </c>
       <c r="F13" t="s">
@@ -890,7 +890,7 @@
         <v>7.91</v>
       </c>
       <c r="E14">
-        <f>D14*60</f>
+        <f t="shared" si="0"/>
         <v>474.6</v>
       </c>
       <c r="F14" t="s">
@@ -911,7 +911,7 @@
         <v>8.1199999999999992</v>
       </c>
       <c r="E15">
-        <f>D15*60</f>
+        <f t="shared" si="0"/>
         <v>487.19999999999993</v>
       </c>
       <c r="F15" t="s">
@@ -932,7 +932,7 @@
         <v>8.2200000000000006</v>
       </c>
       <c r="E16">
-        <f>D16*60</f>
+        <f t="shared" si="0"/>
         <v>493.20000000000005</v>
       </c>
       <c r="F16" t="s">
@@ -953,7 +953,7 @@
         <v>8.5399999999999991</v>
       </c>
       <c r="E17">
-        <f>D17*60</f>
+        <f t="shared" si="0"/>
         <v>512.4</v>
       </c>
       <c r="F17" t="s">
@@ -974,7 +974,7 @@
         <v>8.67</v>
       </c>
       <c r="E18">
-        <f>D18*60</f>
+        <f t="shared" si="0"/>
         <v>520.20000000000005</v>
       </c>
       <c r="F18" t="s">
@@ -995,7 +995,7 @@
         <v>9.82</v>
       </c>
       <c r="E19">
-        <f>D19*60</f>
+        <f t="shared" si="0"/>
         <v>589.20000000000005</v>
       </c>
       <c r="F19" t="s">
@@ -1016,7 +1016,7 @@
         <v>10.01</v>
       </c>
       <c r="E20">
-        <f>D20*60</f>
+        <f t="shared" si="0"/>
         <v>600.6</v>
       </c>
       <c r="F20" t="s">
@@ -1037,7 +1037,7 @@
         <v>11.97</v>
       </c>
       <c r="E21">
-        <f>D21*60</f>
+        <f t="shared" si="0"/>
         <v>718.2</v>
       </c>
       <c r="F21" t="s">
@@ -1058,7 +1058,7 @@
         <v>12.69</v>
       </c>
       <c r="E22">
-        <f>D22*60</f>
+        <f t="shared" si="0"/>
         <v>761.4</v>
       </c>
       <c r="F22" t="s">

--- a/applications/pilot_study/negative/neg_lipid_reference_set.xlsx
+++ b/applications/pilot_study/negative/neg_lipid_reference_set.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/pilot_study/negative/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D1B4F3-9A9F-FD47-9191-1E444CC8F9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98ED6137-685E-0F49-ABAA-4B07F0C5E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17040" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
   <si>
     <t>PC</t>
   </si>
@@ -164,31 +164,34 @@
     <t>PC(18:0/18:2)</t>
   </si>
   <si>
-    <t>Pcnew</t>
-  </si>
-  <si>
     <t>PC(16:0/18:2)</t>
   </si>
   <si>
-    <t>PCnew2</t>
-  </si>
-  <si>
-    <t>LPCnew</t>
-  </si>
-  <si>
-    <t>LPInew</t>
-  </si>
-  <si>
     <t>LPC(18:0/0:0)</t>
   </si>
   <si>
     <t>LPI(20:4/0:0)</t>
   </si>
   <si>
-    <t>PInew</t>
-  </si>
-  <si>
     <t>PI(18:0/18:2)</t>
+  </si>
+  <si>
+    <t>LPI_1</t>
+  </si>
+  <si>
+    <t>LPC_1</t>
+  </si>
+  <si>
+    <t>PI_1</t>
+  </si>
+  <si>
+    <t>PC_1</t>
+  </si>
+  <si>
+    <t>PC_2</t>
+  </si>
+  <si>
+    <t>ISTD</t>
   </si>
 </sst>
 </file>
@@ -198,7 +201,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -207,37 +210,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -252,17 +248,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,471 +603,473 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD69E1-DE54-004B-BA8F-573A6CD4FC04}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" customWidth="1"/>
-    <col min="2" max="2" width="37.5" customWidth="1"/>
+    <col min="1" max="1" width="17.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5" style="1" customWidth="1"/>
+    <col min="3" max="6" width="10.83203125" style="5"/>
+    <col min="7" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="7">
+        <v>619.28890000000001</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1.64</v>
+      </c>
+      <c r="E2" s="5">
+        <f t="shared" ref="E2" si="0">D2*60</f>
+        <v>98.399999999999991</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="7">
+        <v>599.32016833329999</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2.84</v>
+      </c>
+      <c r="E3" s="5">
+        <f>D3*60</f>
+        <v>170.39999999999998</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="7">
+        <v>582.37760000000003</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3.44</v>
+      </c>
+      <c r="E4" s="5">
+        <f>D4*60</f>
+        <v>206.4</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="7">
+        <v>580.36194230119997</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2.56</v>
+      </c>
+      <c r="E5" s="5">
+        <f>D5*60</f>
+        <v>153.6</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="7">
+        <v>452.27820000000003</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2.67</v>
+      </c>
+      <c r="E6" s="5">
+        <f>D6*60</f>
+        <v>160.19999999999999</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="7">
+        <v>861.5498</v>
+      </c>
+      <c r="D7" s="5">
+        <v>7.46</v>
+      </c>
+      <c r="E7" s="5">
+        <f>D7*60</f>
+        <v>447.6</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="4">
-        <v>619.28890000000001</v>
-      </c>
-      <c r="D2">
-        <v>1.64</v>
-      </c>
-      <c r="E2">
-        <f t="shared" ref="E2:E22" si="0">D2*60</f>
-        <v>98.399999999999991</v>
-      </c>
-      <c r="F2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="4">
-        <v>580.36194230119997</v>
-      </c>
-      <c r="D3">
-        <v>2.56</v>
-      </c>
-      <c r="E3">
-        <f t="shared" si="0"/>
-        <v>153.6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="4">
-        <v>452.27820000000003</v>
-      </c>
-      <c r="D4">
-        <v>2.67</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>160.19999999999999</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="7">
+        <v>863.56548436050002</v>
+      </c>
+      <c r="D8" s="5">
+        <v>8.67</v>
+      </c>
+      <c r="E8" s="5">
+        <f>D8*60</f>
+        <v>520.20000000000005</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="7">
+        <v>339.3268314124</v>
+      </c>
+      <c r="D9" s="5">
+        <v>6.34</v>
+      </c>
+      <c r="E9" s="5">
+        <f>D9*60</f>
+        <v>380.4</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="7">
+        <v>844.60730000000001</v>
+      </c>
+      <c r="D10" s="5">
+        <v>10.01</v>
+      </c>
+      <c r="E10" s="5">
+        <f>D10*60</f>
+        <v>600.6</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="7">
+        <v>816.57600000000002</v>
+      </c>
+      <c r="D11" s="5">
+        <v>7.91</v>
+      </c>
+      <c r="E11" s="5">
+        <f>D11*60</f>
+        <v>474.6</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="7">
+        <v>866.59159999999997</v>
+      </c>
+      <c r="D12" s="5">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="E12" s="5">
+        <f>D12*60</f>
+        <v>487.19999999999993</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="7">
+        <v>716.52355807159995</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9.82</v>
+      </c>
+      <c r="E13" s="5">
+        <f>D13*60</f>
+        <v>589.20000000000005</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="7">
+        <v>868.68827192109995</v>
+      </c>
+      <c r="D14" s="5">
+        <v>11.97</v>
+      </c>
+      <c r="E14" s="5">
+        <f>D14*60</f>
+        <v>718.2</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="7">
+        <v>710.66669999999999</v>
+      </c>
+      <c r="D15" s="8">
+        <v>12.69</v>
+      </c>
+      <c r="E15" s="5">
+        <f>D15*60</f>
+        <v>761.4</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C16" s="7">
         <v>587.4058</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D16" s="8">
         <v>2.72</v>
       </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
+      <c r="E16" s="5">
+        <f>D16*60</f>
         <v>163.20000000000002</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F16" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C17" s="7">
         <v>485.33780000000002</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D17" s="8">
         <v>2.83</v>
       </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
+      <c r="E17" s="5">
+        <f>D17*60</f>
         <v>169.8</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F17" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="4">
-        <v>599.32016833329999</v>
-      </c>
-      <c r="D7">
-        <v>2.84</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>170.39999999999998</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="4">
-        <v>582.37760000000003</v>
-      </c>
-      <c r="D8">
-        <v>3.44</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>206.4</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="7">
+        <v>811.61980000000005</v>
+      </c>
+      <c r="D18" s="8">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="E18" s="5">
+        <f>D18*60</f>
+        <v>493.20000000000005</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="7">
+        <v>709.55169999999998</v>
+      </c>
+      <c r="D19" s="8">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="E19" s="5">
+        <f>D19*60</f>
+        <v>512.4</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="7">
+        <v>828.5625</v>
+      </c>
+      <c r="D20" s="8">
+        <v>6.37</v>
+      </c>
+      <c r="E20" s="5">
+        <f>D20*60</f>
+        <v>382.2</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C21" s="7">
         <v>286.42750000000001</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D21" s="8">
         <v>3.5209999999999999</v>
       </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
+      <c r="E21" s="5">
+        <f>D21*60</f>
         <v>211.26</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F21" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C22" s="7">
         <v>422.3503</v>
       </c>
-      <c r="D10">
+      <c r="D22" s="5">
         <v>3.65</v>
       </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
+      <c r="E22" s="5">
+        <f>D22*60</f>
         <v>219</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F22" s="5" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="4">
-        <v>339.3268314124</v>
-      </c>
-      <c r="D11">
-        <v>6.34</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>380.4</v>
-      </c>
-      <c r="F11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4">
-        <v>828.5625</v>
-      </c>
-      <c r="D12" s="3">
-        <v>6.37</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="0"/>
-        <v>382.2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="4">
-        <v>861.5498</v>
-      </c>
-      <c r="D13">
-        <v>7.46</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>447.6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="4">
-        <v>816.57600000000002</v>
-      </c>
-      <c r="D14">
-        <v>7.91</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="0"/>
-        <v>474.6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="4">
-        <v>866.59159999999997</v>
-      </c>
-      <c r="D15">
-        <v>8.1199999999999992</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="0"/>
-        <v>487.19999999999993</v>
-      </c>
-      <c r="F15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="4">
-        <v>811.61980000000005</v>
-      </c>
-      <c r="D16" s="3">
-        <v>8.2200000000000006</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="0"/>
-        <v>493.20000000000005</v>
-      </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="4">
-        <v>709.55169999999998</v>
-      </c>
-      <c r="D17" s="3">
-        <v>8.5399999999999991</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="0"/>
-        <v>512.4</v>
-      </c>
-      <c r="F17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="4">
-        <v>863.56548436050002</v>
-      </c>
-      <c r="D18">
-        <v>8.67</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="0"/>
-        <v>520.20000000000005</v>
-      </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="4">
-        <v>716.52355807159995</v>
-      </c>
-      <c r="D19">
-        <v>9.82</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="0"/>
-        <v>589.20000000000005</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="4">
-        <v>844.60730000000001</v>
-      </c>
-      <c r="D20">
-        <v>10.01</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="0"/>
-        <v>600.6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="4">
-        <v>868.68827192109995</v>
-      </c>
-      <c r="D21">
-        <v>11.97</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="0"/>
-        <v>718.2</v>
-      </c>
-      <c r="F21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="4">
-        <v>710.66669999999999</v>
-      </c>
-      <c r="D22" s="3">
-        <v>12.69</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>761.4</v>
-      </c>
-      <c r="F22" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/applications/pilot_study/negative/neg_lipid_reference_set.xlsx
+++ b/applications/pilot_study/negative/neg_lipid_reference_set.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/pilot_study/negative/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98ED6137-685E-0F49-ABAA-4B07F0C5E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE69B414-2B08-EF4A-9511-3CABD411A755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17040" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
@@ -201,7 +201,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -227,6 +227,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -248,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -266,6 +272,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -666,7 +682,7 @@
         <v>2.84</v>
       </c>
       <c r="E3" s="5">
-        <f>D3*60</f>
+        <f t="shared" ref="E3:E22" si="1">D3*60</f>
         <v>170.39999999999998</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -687,7 +703,7 @@
         <v>3.44</v>
       </c>
       <c r="E4" s="5">
-        <f>D4*60</f>
+        <f t="shared" si="1"/>
         <v>206.4</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -708,7 +724,7 @@
         <v>2.56</v>
       </c>
       <c r="E5" s="5">
-        <f>D5*60</f>
+        <f t="shared" si="1"/>
         <v>153.6</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -729,7 +745,7 @@
         <v>2.67</v>
       </c>
       <c r="E6" s="5">
-        <f>D6*60</f>
+        <f t="shared" si="1"/>
         <v>160.19999999999999</v>
       </c>
       <c r="F6" s="5" t="s">
@@ -750,7 +766,7 @@
         <v>7.46</v>
       </c>
       <c r="E7" s="5">
-        <f>D7*60</f>
+        <f t="shared" si="1"/>
         <v>447.6</v>
       </c>
       <c r="F7" s="5" t="s">
@@ -771,7 +787,7 @@
         <v>8.67</v>
       </c>
       <c r="E8" s="5">
-        <f>D8*60</f>
+        <f t="shared" si="1"/>
         <v>520.20000000000005</v>
       </c>
       <c r="F8" s="5" t="s">
@@ -792,7 +808,7 @@
         <v>6.34</v>
       </c>
       <c r="E9" s="5">
-        <f>D9*60</f>
+        <f t="shared" si="1"/>
         <v>380.4</v>
       </c>
       <c r="F9" s="5" t="s">
@@ -813,7 +829,7 @@
         <v>10.01</v>
       </c>
       <c r="E10" s="5">
-        <f>D10*60</f>
+        <f t="shared" si="1"/>
         <v>600.6</v>
       </c>
       <c r="F10" s="5" t="s">
@@ -834,7 +850,7 @@
         <v>7.91</v>
       </c>
       <c r="E11" s="5">
-        <f>D11*60</f>
+        <f t="shared" si="1"/>
         <v>474.6</v>
       </c>
       <c r="F11" s="5" t="s">
@@ -855,7 +871,7 @@
         <v>8.1199999999999992</v>
       </c>
       <c r="E12" s="5">
-        <f>D12*60</f>
+        <f t="shared" si="1"/>
         <v>487.19999999999993</v>
       </c>
       <c r="F12" s="5" t="s">
@@ -876,7 +892,7 @@
         <v>9.82</v>
       </c>
       <c r="E13" s="5">
-        <f>D13*60</f>
+        <f t="shared" si="1"/>
         <v>589.20000000000005</v>
       </c>
       <c r="F13" s="5" t="s">
@@ -897,7 +913,7 @@
         <v>11.97</v>
       </c>
       <c r="E14" s="5">
-        <f>D14*60</f>
+        <f t="shared" si="1"/>
         <v>718.2</v>
       </c>
       <c r="F14" s="5" t="s">
@@ -918,7 +934,7 @@
         <v>12.69</v>
       </c>
       <c r="E15" s="5">
-        <f>D15*60</f>
+        <f t="shared" si="1"/>
         <v>761.4</v>
       </c>
       <c r="F15" s="5" t="s">
@@ -926,107 +942,107 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="10">
         <v>587.4058</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="11">
         <v>2.72</v>
       </c>
-      <c r="E16" s="5">
-        <f>D16*60</f>
+      <c r="E16" s="12">
+        <f t="shared" si="1"/>
         <v>163.20000000000002</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="12" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="10">
         <v>485.33780000000002</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="11">
         <v>2.83</v>
       </c>
-      <c r="E17" s="5">
-        <f>D17*60</f>
+      <c r="E17" s="12">
+        <f t="shared" si="1"/>
         <v>169.8</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="12" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="10">
         <v>811.61980000000005</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="11">
         <v>8.2200000000000006</v>
       </c>
-      <c r="E18" s="5">
-        <f>D18*60</f>
+      <c r="E18" s="12">
+        <f t="shared" si="1"/>
         <v>493.20000000000005</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="10">
         <v>709.55169999999998</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="11">
         <v>8.5399999999999991</v>
       </c>
-      <c r="E19" s="5">
-        <f>D19*60</f>
+      <c r="E19" s="12">
+        <f t="shared" si="1"/>
         <v>512.4</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="10">
         <v>828.5625</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="11">
         <v>6.37</v>
       </c>
-      <c r="E20" s="5">
-        <f>D20*60</f>
+      <c r="E20" s="12">
+        <f t="shared" si="1"/>
         <v>382.2</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="12" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1044,7 +1060,7 @@
         <v>3.5209999999999999</v>
       </c>
       <c r="E21" s="5">
-        <f>D21*60</f>
+        <f t="shared" si="1"/>
         <v>211.26</v>
       </c>
       <c r="F21" s="5" t="s">
@@ -1052,23 +1068,23 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="10">
         <v>422.3503</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="12">
         <v>3.65</v>
       </c>
-      <c r="E22" s="5">
-        <f>D22*60</f>
+      <c r="E22" s="12">
+        <f t="shared" si="1"/>
         <v>219</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="12" t="s">
         <v>29</v>
       </c>
     </row>
